--- a/2022-2023/Data og lign/IQdata.xlsx
+++ b/2022-2023/Data og lign/IQdata.xlsx
@@ -384,867 +384,867 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>169</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3">
-        <v>156</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4">
-        <v>170</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5">
-        <v>179</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6">
-        <v>171</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7">
-        <v>167</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8">
-        <v>179</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9">
-        <v>165</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10">
-        <v>170</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>167</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>178</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>159</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>172</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>168</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>166</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>171</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>171</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>166</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>163</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>171</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>171</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>168</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>160</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25">
-        <v>173</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>166</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>174</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>180</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29">
-        <v>165</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30">
-        <v>156</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31">
-        <v>152</v>
+        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32">
-        <v>162</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>166</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34">
-        <v>169</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35">
-        <v>167</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36">
-        <v>167</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37">
-        <v>175</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>179</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>163</v>
+        <v>129</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>171</v>
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>170</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>162</v>
+        <v>114</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>172</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>160</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>163</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>165</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47">
-        <v>169</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48">
-        <v>163</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49">
-        <v>167</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50">
-        <v>168</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51">
-        <v>164</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52">
-        <v>162</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>156</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>154</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55">
-        <v>178</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56">
-        <v>175</v>
+        <v>102</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57">
-        <v>171</v>
+        <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58">
-        <v>151</v>
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59">
-        <v>167</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60">
-        <v>164</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61">
-        <v>155</v>
+        <v>114</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62">
-        <v>170</v>
+        <v>95</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63">
-        <v>163</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64">
-        <v>157</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>167</v>
+        <v>108</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>152</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>175</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>169</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>173</v>
+        <v>108</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71">
-        <v>167</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72">
-        <v>171</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>160</v>
+        <v>116</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>161</v>
+        <v>115</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>175</v>
+        <v>115</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>168</v>
+        <v>119</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>171</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>173</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>166</v>
+        <v>97</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>163</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>158</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>171</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
-        <v>149</v>
+        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84">
-        <v>170</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
-        <v>161</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86">
-        <v>163</v>
+        <v>79</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87">
-        <v>171</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88">
-        <v>178</v>
+        <v>88</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>167</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>190</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>172</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>159</v>
+        <v>102</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>174</v>
+        <v>110</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>176</v>
+        <v>104</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>156</v>
+        <v>86</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>173</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98">
-        <v>172</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99">
-        <v>165</v>
+        <v>112</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100">
-        <v>166</v>
+        <v>90</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
-        <v>164</v>
+        <v>91</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102">
-        <v>164</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103">
-        <v>170</v>
+        <v>70</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104">
-        <v>160</v>
+        <v>92</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105">
-        <v>170</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106">
-        <v>161</v>
+        <v>71</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107">
-        <v>160</v>
+        <v>89</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108">
-        <v>167</v>
+        <v>109</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109">
-        <v>181</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110">
-        <v>166</v>
+        <v>123</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111">
-        <v>168</v>
+        <v>111</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112">
-        <v>162</v>
+        <v>85</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113">
-        <v>157</v>
+        <v>116</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114">
-        <v>164</v>
+        <v>95</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115">
-        <v>165</v>
+        <v>65</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116">
-        <v>162</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117">
-        <v>166</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118">
-        <v>173</v>
+        <v>93</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119">
-        <v>176</v>
+        <v>111</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120">
-        <v>177</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121">
-        <v>166</v>
+        <v>82</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123">
-        <v>178</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124">
-        <v>176</v>
+        <v>112</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125">
-        <v>157</v>
+        <v>112</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126">
-        <v>167</v>
+        <v>86</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127">
-        <v>165</v>
+        <v>103</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128">
-        <v>162</v>
+        <v>106</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129">
-        <v>163</v>
+        <v>128</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130">
-        <v>160</v>
+        <v>97</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131">
-        <v>163</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132">
-        <v>167</v>
+        <v>98</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133">
-        <v>174</v>
+        <v>82</v>
       </c>
     </row>
     <row r="134" spans="1:1">
       <c r="A134">
-        <v>164</v>
+        <v>108</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135">
-        <v>167</v>
+        <v>79</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136">
-        <v>165</v>
+        <v>107</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137">
-        <v>159</v>
+        <v>119</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138">
-        <v>168</v>
+        <v>91</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139">
-        <v>159</v>
+        <v>89</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140">
-        <v>169</v>
+        <v>71</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141">
-        <v>185</v>
+        <v>124</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142">
-        <v>180</v>
+        <v>92</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143">
-        <v>167</v>
+        <v>127</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144">
-        <v>172</v>
+        <v>107</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145">
-        <v>167</v>
+        <v>108</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146">
-        <v>175</v>
+        <v>127</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147">
-        <v>171</v>
+        <v>107</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148">
-        <v>174</v>
+        <v>116</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149">
-        <v>160</v>
+        <v>91</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150">
-        <v>158</v>
+        <v>126</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151">
-        <v>173</v>
+        <v>107</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152">
-        <v>181</v>
+        <v>91</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153">
-        <v>163</v>
+        <v>107</v>
       </c>
     </row>
     <row r="154" spans="1:1">
       <c r="A154">
-        <v>166</v>
+        <v>91</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155">
-        <v>161</v>
+        <v>105</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156">
-        <v>160</v>
+        <v>108</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157">
-        <v>178</v>
+        <v>79</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158">
-        <v>172</v>
+        <v>111</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159">
-        <v>160</v>
+        <v>107</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160">
-        <v>169</v>
+        <v>111</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161">
-        <v>163</v>
+        <v>112</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162">
-        <v>166</v>
+        <v>86</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163">
-        <v>166</v>
+        <v>132</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164">
-        <v>162</v>
+        <v>117</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165">
-        <v>171</v>
+        <v>101</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166">
-        <v>182</v>
+        <v>110</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167">
-        <v>171</v>
+        <v>99</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168">
-        <v>175</v>
+        <v>82</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169">
-        <v>179</v>
+        <v>81</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170">
-        <v>172</v>
+        <v>125</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171">
-        <v>173</v>
+        <v>88</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172">
-        <v>156</v>
+        <v>110</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173">
-        <v>169</v>
+        <v>88</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174">
-        <v>170</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
